--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -895,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2317,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2365,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2384,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2409,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2420,1026 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,17 +1288,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1304,13 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1371,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1449,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1482,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,17 +1526,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1526,13 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1593,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1704,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1854,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1893,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1926,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1950,33 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2004,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2037,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2061,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2115,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2148,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2172,17 +2232,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2192,13 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2226,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2259,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2283,33 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2535,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2635,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2707,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2746,7 +2818,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2761,7 +2833,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2861,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2876,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2937,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2991,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3278,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3322,13 +3394,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3433,13 +3509,1159 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2520,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,17 +2581,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2597,7 +2601,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2779,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,17 +2811,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2823,17 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,32 +2984,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3009,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3033,37 +3045,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3091,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3124,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3148,37 +3164,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3350,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3520,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3580,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3619,7 +3635,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3695,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3810,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3979,7 +3995,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4205,7 +4221,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4282,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4397,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4508,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4623,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4651,17 +4667,477 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3448,32 +3448,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3481,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,17 +3509,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3525,17 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3563,32 +3567,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3596,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3620,17 +3628,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3640,17 +3648,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,7 +3758,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3765,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3793,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3826,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3870,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3995,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4095,7 +4107,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4167,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4218,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4282,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4635,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4677,7 +4689,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4750,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4865,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4907,7 +4919,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4980,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5012,17 +5024,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5095,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5127,17 +5139,358 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>11/18</t>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,13 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2370,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,13 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3524,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3539,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3658,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3811,24 +3819,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,12 +3895,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3953,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,32 +3989,32 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4035,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4068,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4092,17 +4108,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4112,13 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4146,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4179,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4203,17 +4227,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4223,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4261,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4294,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4318,37 +4346,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4404,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4409,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4433,17 +4465,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4453,13 +4485,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4487,32 +4523,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4520,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4544,37 +4584,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4602,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4635,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,37 +4703,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4717,32 +4761,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4750,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4774,37 +4822,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4919,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5019,7 +5067,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5034,7 +5082,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5149,7 +5197,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5264,7 +5312,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5272,22 +5320,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5325,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5339,7 +5387,7 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5369,13 +5417,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5435,7 @@
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5393,7 +5445,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5431,12 +5483,12 @@
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5450,47 +5502,737 @@
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr">
         <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>11:35</t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr">
+      <c r="W45" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z43" s="2" t="inlineStr">
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>90.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4771,24 +4771,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4995,32 +4995,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5052,17 +5056,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5072,12 +5076,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5110,32 +5114,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5143,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,37 +5175,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5340,32 +5348,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5373,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5397,32 +5409,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5455,32 +5467,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5488,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5512,32 +5528,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5570,32 +5586,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5603,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,32 +5647,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5718,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5777,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5833,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5948,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6112,12 +6132,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,17 +6242,592 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>5/18</t>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,17 +4837,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5358,24 +5358,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5477,24 +5477,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5596,24 +5596,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5705,32 +5705,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5738,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,17 +5766,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5782,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5820,32 +5824,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5853,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,37 +5885,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5943,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5968,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5992,37 +6004,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6050,32 +6062,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6083,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6107,32 +6123,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6165,32 +6181,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6198,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6222,37 +6242,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6428,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6477,12 +6497,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6592,12 +6612,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6678,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6707,7 +6727,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6773,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6817,17 +6837,592 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>89.5</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,14 +2251,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,22 +5424,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,17 +5543,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6300,32 +6300,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6333,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6357,37 +6361,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6415,32 +6419,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6448,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6472,37 +6480,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6530,32 +6538,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6563,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6587,32 +6599,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6645,32 +6657,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6678,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6702,17 +6718,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6722,12 +6738,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6760,32 +6776,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6793,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6817,17 +6837,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6837,17 +6857,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6908,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7023,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7187,12 +7207,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7388,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7417,12 +7437,472 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,22 +4599,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,17 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,17 +5662,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,17 +6143,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,17 +6262,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6667,24 +6667,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6733,17 +6733,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6895,32 +6895,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6928,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6952,37 +6956,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7010,32 +7014,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7043,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7067,37 +7075,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7125,32 +7133,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7158,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7182,17 +7194,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7202,17 +7214,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7327,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7355,32 +7367,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7388,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7412,17 +7428,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7432,17 +7448,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7618,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7672,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7795,22 +7811,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7843,12 +7859,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7887,22 +7903,1053 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
+      <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,17 +3413,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,17 +4004,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5274,10 +5274,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq20（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq20映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5305,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5320,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,17 +5436,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5504,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5742,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5861,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5980,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6099,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6218,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6376,7 +6388,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6391,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,17 +6507,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6575,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6733,7 +6745,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6932,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,7 +7221,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7252,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7285,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,37 +7325,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7389,12 +7405,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7404,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7443,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7519,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7558,7 +7574,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7573,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7601,32 +7617,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7634,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7658,32 +7678,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7716,32 +7736,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7749,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7773,37 +7797,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7831,32 +7855,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7864,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7888,32 +7916,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7946,32 +7974,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7979,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8003,37 +8035,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8133,7 +8165,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8209,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8604,7 +8636,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8697,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8780,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8834,7 +8866,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8927,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8953,6 +8985,1156 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>91.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,17 +2949,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,22 +4480,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,17 +4599,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,17 +4718,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,22 +4952,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8093,32 +8093,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8126,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8150,17 +8154,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8170,17 +8174,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8208,32 +8212,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8241,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,37 +8273,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8395,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8434,32 +8442,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8467,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8491,32 +8503,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8549,32 +8561,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8582,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8606,37 +8622,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8664,32 +8680,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8697,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8721,37 +8741,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8779,32 +8799,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8812,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8836,32 +8860,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8894,32 +8918,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8927,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8951,32 +8979,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9009,32 +9037,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9042,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9066,37 +9098,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9211,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9311,7 +9343,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9387,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9502,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9617,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9671,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9847,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9901,7 +9933,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10077,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10121,17 +10153,1048 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>2/18</t>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2251,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,22 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,22 +4123,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,22 +5555,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6150,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6393,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,22 +7693,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,22 +8050,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9047,24 +9047,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9156,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9189,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,37 +9217,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9271,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9304,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9328,17 +9336,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9348,12 +9356,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9419,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9458,7 +9466,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9473,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9501,32 +9509,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9534,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9558,37 +9570,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9616,32 +9628,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9649,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9673,17 +9689,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9693,17 +9709,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9731,32 +9747,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9764,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9788,37 +9808,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9846,32 +9866,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9879,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9903,37 +9927,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10033,7 +10057,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10109,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10224,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10278,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10339,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10378,7 +10402,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10450,7 +10474,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10504,7 +10528,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10565,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10604,7 +10628,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10680,7 +10704,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10734,7 +10758,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10795,7 +10819,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10849,7 +10873,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11025,7 +11049,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11069,12 +11093,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11140,7 +11164,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11189,12 +11213,928 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>92.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2137,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,13 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,17 +3770,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3900,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4251,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,22 +4484,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4608,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5086,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6284,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6992,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7355,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7474,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7892,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8249,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8288,7 +8292,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8303,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,13 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8756,22 +8764,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,17 +8888,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9113,17 +9121,17 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9193,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9247,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9366,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9466,7 +9474,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9481,7 +9489,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9719,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9903,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9957,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10072,7 +10080,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10248,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10287,7 +10295,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10302,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10330,32 +10338,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10363,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10387,17 +10399,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10407,13 +10419,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB84" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10441,32 +10457,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10474,7 +10494,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10498,17 +10518,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10518,17 +10538,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10556,32 +10576,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10589,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10613,17 +10637,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10633,17 +10657,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10671,32 +10695,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10704,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10728,37 +10756,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10786,32 +10814,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10819,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10843,17 +10875,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10863,17 +10895,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10988,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11049,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11103,7 +11135,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11131,32 +11163,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11164,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11188,32 +11224,32 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11279,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11333,7 +11369,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11509,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11548,7 +11584,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11563,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11678,7 +11714,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11775,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11854,7 +11890,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11898,13 +11934,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11965,7 +12005,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12019,7 +12059,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12124,17 +12164,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>91.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>7/18</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>93.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,22 +7935,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9364,17 +9364,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,17 +9836,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10065,22 +10065,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10295,7 +10295,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10419,17 +10419,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11048,32 +11048,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11081,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11105,17 +11109,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11125,17 +11129,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11254,7 +11258,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11282,32 +11286,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11315,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11339,17 +11347,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11359,12 +11367,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11397,32 +11405,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11430,7 +11442,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11454,17 +11466,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11474,17 +11486,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11512,32 +11524,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11545,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11569,17 +11585,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11589,17 +11605,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11627,32 +11643,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11660,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11684,17 +11704,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11704,12 +11724,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11742,32 +11762,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11775,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,17 +11823,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11819,17 +11843,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11857,32 +11881,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11890,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11914,17 +11942,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11934,17 +11962,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11972,32 +12000,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12005,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12029,37 +12061,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12087,32 +12119,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12120,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12144,17 +12180,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12164,17 +12200,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12271,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12274,7 +12310,7 @@
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
@@ -12289,7 +12325,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12386,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12404,7 +12440,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12504,7 +12540,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12519,7 +12555,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12624,17 +12660,362 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB103" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC103" s="2" t="inlineStr">
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4489,17 +4489,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,17 +9126,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,17 +9479,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9846,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,17 +10776,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11248,17 +11248,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,17 +11605,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12238,32 +12238,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12271,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12295,17 +12299,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12315,17 +12319,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12353,32 +12357,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12386,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12410,17 +12418,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12430,17 +12438,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12468,32 +12476,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12501,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12525,17 +12537,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12545,17 +12557,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12583,32 +12595,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12616,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12640,17 +12656,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12660,17 +12676,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12747,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12785,7 +12801,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12862,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12890,17 +12906,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12961,7 +12977,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13005,17 +13021,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-30-浦东78路.xlsx
+++ b/data/export/2026-10-30-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9484,12 +9484,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10070,17 +10070,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10300,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11610,12 +11610,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12081,17 +12081,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12319,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12605,24 +12605,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12681,12 +12681,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12714,32 +12714,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12747,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12771,17 +12775,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12791,17 +12795,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12829,32 +12833,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12862,7 +12870,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12886,17 +12894,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12906,17 +12914,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12985,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13031,7 +13039,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
